--- a/excel/sales_targets.xlsx
+++ b/excel/sales_targets.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1056d8d355350218/Desktop/work/denodo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TakumaMatsuo\Desktop\Denodo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{FCF2EB95-750E-4901-BF0A-12993A4B73A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DECC349C-0CA9-4E13-9E99-A9B79B1D9871}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8469E63A-3A26-46D1-A332-854BCBF1D696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8385" yWindow="1605" windowWidth="29295" windowHeight="21630" xr2:uid="{6CC2BA7A-2587-4AFC-B95E-A4295AD7B88E}"/>
+    <workbookView xWindow="345" yWindow="405" windowWidth="25050" windowHeight="14805" xr2:uid="{6CC2BA7A-2587-4AFC-B95E-A4295AD7B88E}"/>
   </bookViews>
   <sheets>
     <sheet name="TargetData" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TargetData!$A$1:$D$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TargetData!$A$1:$D$109</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="9">
   <si>
     <t>target_month</t>
   </si>
@@ -753,10 +753,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1076,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8429390A-C0D2-4CBC-A0B7-66EB33143C03}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
@@ -1101,7 +1097,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" s="2">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -1115,7 +1111,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1129,7 +1125,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1143,7 +1139,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -1157,7 +1153,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
-        <v>46113</v>
+        <v>45748</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -1171,7 +1167,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -1186,7 +1182,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -1201,7 +1197,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B9" s="1">
         <v>3</v>
@@ -1216,7 +1212,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B10" s="1">
         <v>4</v>
@@ -1231,7 +1227,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
-        <v>46143</v>
+        <v>45778</v>
       </c>
       <c r="B11" s="1">
         <v>5</v>
@@ -1246,7 +1242,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="1">
         <v>1</v>
@@ -1261,7 +1257,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
@@ -1276,7 +1272,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="1">
         <v>3</v>
@@ -1291,7 +1287,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B15" s="1">
         <v>4</v>
@@ -1306,7 +1302,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
-        <v>46174</v>
+        <v>45809</v>
       </c>
       <c r="B16" s="1">
         <v>5</v>
@@ -1321,7 +1317,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B17" s="1">
         <v>1</v>
@@ -1336,7 +1332,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B18" s="1">
         <v>2</v>
@@ -1351,7 +1347,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B19" s="1">
         <v>3</v>
@@ -1366,7 +1362,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B20" s="1">
         <v>4</v>
@@ -1381,7 +1377,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
-        <v>46204</v>
+        <v>45839</v>
       </c>
       <c r="B21" s="1">
         <v>5</v>
@@ -1396,7 +1392,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
-        <v>46235</v>
+        <v>45870</v>
       </c>
       <c r="B22" s="1">
         <v>1</v>
@@ -1411,7 +1407,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
-        <v>46235</v>
+        <v>45870</v>
       </c>
       <c r="B23" s="1">
         <v>2</v>
@@ -1426,7 +1422,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
-        <v>46235</v>
+        <v>45870</v>
       </c>
       <c r="B24" s="1">
         <v>3</v>
@@ -1441,7 +1437,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
-        <v>46235</v>
+        <v>45870</v>
       </c>
       <c r="B25" s="1">
         <v>4</v>
@@ -1456,7 +1452,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
-        <v>46235</v>
+        <v>45870</v>
       </c>
       <c r="B26" s="1">
         <v>5</v>
@@ -1471,7 +1467,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B27" s="1">
         <v>1</v>
@@ -1486,7 +1482,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B28" s="1">
         <v>2</v>
@@ -1501,7 +1497,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B29" s="1">
         <v>3</v>
@@ -1516,7 +1512,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B30" s="1">
         <v>4</v>
@@ -1531,7 +1527,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
-        <v>46266</v>
+        <v>45901</v>
       </c>
       <c r="B31" s="1">
         <v>5</v>
@@ -1546,7 +1542,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B32" s="1">
         <v>1</v>
@@ -1561,7 +1557,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B33" s="1">
         <v>2</v>
@@ -1576,7 +1572,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B34" s="1">
         <v>3</v>
@@ -1591,7 +1587,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B35" s="1">
         <v>4</v>
@@ -1606,7 +1602,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
-        <v>46296</v>
+        <v>45931</v>
       </c>
       <c r="B36" s="1">
         <v>5</v>
@@ -1621,7 +1617,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
-        <v>46327</v>
+        <v>45962</v>
       </c>
       <c r="B37" s="1">
         <v>1</v>
@@ -1636,7 +1632,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
-        <v>46327</v>
+        <v>45962</v>
       </c>
       <c r="B38" s="1">
         <v>2</v>
@@ -1651,7 +1647,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
-        <v>46327</v>
+        <v>45962</v>
       </c>
       <c r="B39" s="1">
         <v>3</v>
@@ -1666,7 +1662,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
-        <v>46327</v>
+        <v>45962</v>
       </c>
       <c r="B40" s="1">
         <v>4</v>
@@ -1681,7 +1677,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
-        <v>46327</v>
+        <v>45962</v>
       </c>
       <c r="B41" s="1">
         <v>5</v>
@@ -1696,7 +1692,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B42" s="1">
         <v>1</v>
@@ -1711,7 +1707,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B43" s="1">
         <v>2</v>
@@ -1726,7 +1722,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B44" s="1">
         <v>3</v>
@@ -1741,7 +1737,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B45" s="1">
         <v>4</v>
@@ -1756,7 +1752,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
-        <v>46357</v>
+        <v>45992</v>
       </c>
       <c r="B46" s="1">
         <v>5</v>
@@ -1771,7 +1767,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
-        <v>46388</v>
+        <v>46023</v>
       </c>
       <c r="B47" s="1">
         <v>1</v>
@@ -1786,7 +1782,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
-        <v>46388</v>
+        <v>46023</v>
       </c>
       <c r="B48" s="1">
         <v>2</v>
@@ -1801,7 +1797,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
-        <v>46388</v>
+        <v>46023</v>
       </c>
       <c r="B49" s="1">
         <v>3</v>
@@ -1816,7 +1812,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
-        <v>46388</v>
+        <v>46023</v>
       </c>
       <c r="B50" s="1">
         <v>4</v>
@@ -1831,7 +1827,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
-        <v>46388</v>
+        <v>46023</v>
       </c>
       <c r="B51" s="1">
         <v>5</v>
@@ -1846,7 +1842,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
@@ -1861,7 +1857,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B53" s="1">
         <v>2</v>
@@ -1876,7 +1872,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B54" s="1">
         <v>3</v>
@@ -1891,7 +1887,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B55" s="1">
         <v>4</v>
@@ -1906,7 +1902,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
-        <v>46419</v>
+        <v>46054</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
@@ -1921,7 +1917,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
-        <v>46447</v>
+        <v>46082</v>
       </c>
       <c r="B57" s="1">
         <v>1</v>
@@ -1936,7 +1932,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
-        <v>46447</v>
+        <v>46082</v>
       </c>
       <c r="B58" s="1">
         <v>2</v>
@@ -1951,7 +1947,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
-        <v>46447</v>
+        <v>46082</v>
       </c>
       <c r="B59" s="1">
         <v>3</v>
@@ -1966,7 +1962,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
-        <v>46447</v>
+        <v>46082</v>
       </c>
       <c r="B60" s="1">
         <v>4</v>
@@ -1981,7 +1977,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
-        <v>46447</v>
+        <v>46082</v>
       </c>
       <c r="B61" s="1">
         <v>5</v>
@@ -1994,8 +1990,903 @@
         <v>5578341.7333265822</v>
       </c>
     </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A62" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D62" s="4">
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A63" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="4">
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A64" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B64" s="1">
+        <v>3</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="4">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A65" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B65" s="1">
+        <v>4</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="4">
+        <v>15000000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A66" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B66" s="1">
+        <v>5</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="4">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A67" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B67" s="1">
+        <v>1</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D67" s="4">
+        <f>D62*1.01</f>
+        <v>50500000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A68" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" s="4">
+        <f t="shared" ref="D68:D121" si="1">D63*1.01</f>
+        <v>30300000</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A69" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B69" s="1">
+        <v>3</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="4">
+        <f t="shared" si="1"/>
+        <v>10100000</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A70" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B70" s="1">
+        <v>4</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4">
+        <f t="shared" si="1"/>
+        <v>15150000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A71" s="2">
+        <v>46143</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" s="4">
+        <f t="shared" si="1"/>
+        <v>5050000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A72" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" s="4">
+        <f t="shared" si="1"/>
+        <v>51005000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A73" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" s="4">
+        <f t="shared" si="1"/>
+        <v>30603000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A74" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="4">
+        <f t="shared" si="1"/>
+        <v>10201000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A75" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B75" s="1">
+        <v>4</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="4">
+        <f t="shared" si="1"/>
+        <v>15301500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A76" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B76" s="1">
+        <v>5</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="4">
+        <f t="shared" si="1"/>
+        <v>5100500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A77" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B77" s="1">
+        <v>1</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="4">
+        <f t="shared" si="1"/>
+        <v>51515050</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A78" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="4">
+        <f t="shared" si="1"/>
+        <v>30909030</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A79" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B79" s="1">
+        <v>3</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="4">
+        <f t="shared" si="1"/>
+        <v>10303010</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A80" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="4">
+        <f t="shared" si="1"/>
+        <v>15454515</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A81" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B81" s="1">
+        <v>5</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D81" s="4">
+        <f t="shared" si="1"/>
+        <v>5151505</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A82" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B82" s="1">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="4">
+        <f t="shared" si="1"/>
+        <v>52030200.5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A83" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B83" s="1">
+        <v>2</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D83" s="4">
+        <f t="shared" si="1"/>
+        <v>31218120.300000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A84" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B84" s="1">
+        <v>3</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="4">
+        <f t="shared" si="1"/>
+        <v>10406040.1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A85" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="4">
+        <f t="shared" si="1"/>
+        <v>15609060.15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A86" s="2">
+        <v>46235</v>
+      </c>
+      <c r="B86" s="1">
+        <v>5</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" s="4">
+        <f t="shared" si="1"/>
+        <v>5203020.05</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A87" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="4">
+        <f t="shared" si="1"/>
+        <v>52550502.505000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A88" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B88" s="1">
+        <v>2</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="1"/>
+        <v>31530301.503000002</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A89" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B89" s="1">
+        <v>3</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="4">
+        <f t="shared" si="1"/>
+        <v>10510100.501</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A90" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="4">
+        <f t="shared" si="1"/>
+        <v>15765150.751500001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A91" s="2">
+        <v>46266</v>
+      </c>
+      <c r="B91" s="1">
+        <v>5</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="4">
+        <f t="shared" si="1"/>
+        <v>5255050.2505000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A92" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B92" s="1">
+        <v>1</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" s="4">
+        <f t="shared" si="1"/>
+        <v>53076007.530050002</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A93" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B93" s="1">
+        <v>2</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="4">
+        <f t="shared" si="1"/>
+        <v>31845604.518030003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A94" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B94" s="1">
+        <v>3</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="4">
+        <f t="shared" si="1"/>
+        <v>10615201.50601</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A95" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="4">
+        <f t="shared" si="1"/>
+        <v>15922802.259015001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A96" s="2">
+        <v>46296</v>
+      </c>
+      <c r="B96" s="1">
+        <v>5</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D96" s="4">
+        <f t="shared" si="1"/>
+        <v>5307600.7530049998</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A97" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B97" s="1">
+        <v>1</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D97" s="4">
+        <f t="shared" si="1"/>
+        <v>53606767.605350502</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A98" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B98" s="1">
+        <v>2</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D98" s="4">
+        <f t="shared" si="1"/>
+        <v>32164060.563210305</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A99" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B99" s="1">
+        <v>3</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="4">
+        <f t="shared" si="1"/>
+        <v>10721353.5210701</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A100" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="4">
+        <f t="shared" si="1"/>
+        <v>16082030.281605152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A101" s="2">
+        <v>46327</v>
+      </c>
+      <c r="B101" s="1">
+        <v>5</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" s="4">
+        <f t="shared" si="1"/>
+        <v>5360676.7605350502</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A102" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B102" s="1">
+        <v>1</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D102" s="4">
+        <f t="shared" si="1"/>
+        <v>54142835.281404011</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A103" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D103" s="4">
+        <f t="shared" si="1"/>
+        <v>32485701.168842409</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A104" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B104" s="1">
+        <v>3</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" s="4">
+        <f t="shared" si="1"/>
+        <v>10828567.056280801</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A105" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="4">
+        <f t="shared" si="1"/>
+        <v>16242850.584421204</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A106" s="2">
+        <v>46357</v>
+      </c>
+      <c r="B106" s="1">
+        <v>5</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" s="4">
+        <f t="shared" si="1"/>
+        <v>5414283.5281404005</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A107" s="2">
+        <v>46388</v>
+      </c>
+      <c r="B107" s="1">
+        <v>1</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D107" s="4">
+        <f t="shared" si="1"/>
+        <v>54684263.634218052</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A108" s="2">
+        <v>46388</v>
+      </c>
+      <c r="B108" s="1">
+        <v>2</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D108" s="4">
+        <f t="shared" si="1"/>
+        <v>32810558.180530835</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A109" s="2">
+        <v>46388</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="4">
+        <f t="shared" si="1"/>
+        <v>10936852.726843609</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A110" s="2">
+        <v>46388</v>
+      </c>
+      <c r="B110" s="1">
+        <v>4</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="4">
+        <f t="shared" si="1"/>
+        <v>16405279.090265417</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A111" s="2">
+        <v>46388</v>
+      </c>
+      <c r="B111" s="1">
+        <v>5</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="4">
+        <f t="shared" si="1"/>
+        <v>5468426.3634218043</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A112" s="2">
+        <v>46419</v>
+      </c>
+      <c r="B112" s="1">
+        <v>1</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="4">
+        <f t="shared" si="1"/>
+        <v>55231106.270560235</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A113" s="2">
+        <v>46419</v>
+      </c>
+      <c r="B113" s="1">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D113" s="4">
+        <f t="shared" si="1"/>
+        <v>33138663.762336142</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A114" s="2">
+        <v>46419</v>
+      </c>
+      <c r="B114" s="1">
+        <v>3</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="4">
+        <f t="shared" si="1"/>
+        <v>11046221.254112044</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A115" s="2">
+        <v>46419</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" s="4">
+        <f t="shared" si="1"/>
+        <v>16569331.881168071</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A116" s="2">
+        <v>46419</v>
+      </c>
+      <c r="B116" s="1">
+        <v>5</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" s="4">
+        <f t="shared" si="1"/>
+        <v>5523110.6270560222</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A117" s="2">
+        <v>46447</v>
+      </c>
+      <c r="B117" s="1">
+        <v>1</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="4">
+        <f t="shared" si="1"/>
+        <v>55783417.333265841</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A118" s="2">
+        <v>46447</v>
+      </c>
+      <c r="B118" s="1">
+        <v>2</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" s="4">
+        <f t="shared" si="1"/>
+        <v>33470050.399959505</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A119" s="2">
+        <v>46447</v>
+      </c>
+      <c r="B119" s="1">
+        <v>3</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="4">
+        <f t="shared" si="1"/>
+        <v>11156683.466653164</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A120" s="2">
+        <v>46447</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" s="4">
+        <f t="shared" si="1"/>
+        <v>16735025.199979752</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A121" s="2">
+        <v>46447</v>
+      </c>
+      <c r="B121" s="1">
+        <v>5</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="4">
+        <f t="shared" si="1"/>
+        <v>5578341.7333265822</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D49" xr:uid="{8429390A-C0D2-4CBC-A0B7-66EB33143C03}"/>
+  <autoFilter ref="A1:D109" xr:uid="{8429390A-C0D2-4CBC-A0B7-66EB33143C03}"/>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
